--- a/Result/profitability/5203.xlsx
+++ b/Result/profitability/5203.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM78"/>
+  <dimension ref="A1:AM79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
         <v>2.72</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1675</v>
+        <v>1.13875</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -762,7 +762,7 @@
         <v>2.19</v>
       </c>
       <c r="M3" t="n">
-        <v>1.37125</v>
+        <v>1.27625</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -873,7 +873,7 @@
         <v>2.41</v>
       </c>
       <c r="M4" t="n">
-        <v>1.53625</v>
+        <v>1.41625</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -984,7 +984,7 @@
         <v>3.03</v>
       </c>
       <c r="M5" t="n">
-        <v>1.75375</v>
+        <v>1.8425</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>96.40000000000001</v>
@@ -1101,7 +1101,7 @@
         <v>2.08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.06125</v>
+        <v>1.89375</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1222,7 +1222,7 @@
         <v>2.31</v>
       </c>
       <c r="M7" t="n">
-        <v>2.14125</v>
+        <v>2.05125</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1343,7 +1343,7 @@
         <v>2.89</v>
       </c>
       <c r="M8" t="n">
-        <v>2.37125</v>
+        <v>2.245</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -9793,13 +9793,13 @@
         <v>599</v>
       </c>
       <c r="D75" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E75" t="n">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="F75" t="n">
-        <v>87.03</v>
+        <v>85.8</v>
       </c>
       <c r="G75" t="n">
         <v>91</v>
@@ -9825,7 +9825,7 @@
         <v>0.78</v>
       </c>
       <c r="N75" t="n">
-        <v>85.14749999999999</v>
+        <v>84.99375000000001</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9837,7 +9837,7 @@
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -9858,10 +9858,10 @@
         <v>-1.294573643410853</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.980000000000004</v>
+        <v>1.75</v>
       </c>
       <c r="Z75" t="n">
-        <v>0.03545508625817972</v>
+        <v>0.0208209399167163</v>
       </c>
       <c r="AA75" t="n">
         <v>-1.46</v>
@@ -9870,10 +9870,10 @@
         <v>-1.351851851851852</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.010000000000005</v>
+        <v>-0.2199999999999989</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.0117414554754709</v>
+        <v>-0.002557544757033181</v>
       </c>
       <c r="AE75" t="n">
         <v>0</v>
@@ -9885,14 +9885,14 @@
         <v>1</v>
       </c>
       <c r="AH75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>EPS衰退 / 毛利率成長</t>
+          <t>EPS衰退 / 毛利率衰退</t>
         </is>
       </c>
       <c r="AK75" t="n">
@@ -9920,13 +9920,13 @@
         <v>636</v>
       </c>
       <c r="D76" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E76" t="n">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="F76" t="n">
-        <v>83.48999999999999</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="G76" t="n">
         <v>92</v>
@@ -9952,7 +9952,7 @@
         <v>0.8387500000000001</v>
       </c>
       <c r="N76" t="n">
-        <v>84.8325</v>
+        <v>84.82375</v>
       </c>
       <c r="O76" t="n">
         <v>1</v>
@@ -9985,10 +9985,10 @@
         <v>-5.394736842105263</v>
       </c>
       <c r="Y76" t="n">
-        <v>-3.540000000000006</v>
+        <v>-1.149999999999991</v>
       </c>
       <c r="Z76" t="n">
-        <v>-0.04067562909341615</v>
+        <v>-0.01340326340326325</v>
       </c>
       <c r="AA76" t="n">
         <v>1.11</v>
@@ -9997,10 +9997,10 @@
         <v>1.982142857142857</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.469999999999999</v>
+        <v>2.63000000000001</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.01792245793708847</v>
+        <v>0.03206534991465504</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -10079,7 +10079,7 @@
         <v>0.9525</v>
       </c>
       <c r="N77" t="n">
-        <v>84.49250000000001</v>
+        <v>84.48375</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
@@ -10112,10 +10112,10 @@
         <v>-0.37125748502994</v>
       </c>
       <c r="Y77" t="n">
-        <v>-0.04999999999999716</v>
+        <v>-1.210000000000008</v>
       </c>
       <c r="Z77" t="n">
-        <v>-0.0005988741166605971</v>
+        <v>-0.01429415239220333</v>
       </c>
       <c r="AA77" t="n">
         <v>-0.04000000000000004</v>
@@ -10206,7 +10206,7 @@
         <v>0.9625</v>
       </c>
       <c r="N78" t="n">
-        <v>84.33</v>
+        <v>84.32124999999999</v>
       </c>
       <c r="O78" t="n">
         <v>1</v>
@@ -10284,6 +10284,133 @@
       </c>
       <c r="AM78" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>528</v>
+      </c>
+      <c r="D79" t="n">
+        <v>77</v>
+      </c>
+      <c r="E79" t="n">
+        <v>451</v>
+      </c>
+      <c r="F79" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="G79" t="n">
+        <v>18</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>29</v>
+      </c>
+      <c r="J79" t="n">
+        <v>47</v>
+      </c>
+      <c r="K79" t="n">
+        <v>26</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.86875</v>
+      </c>
+      <c r="N79" t="n">
+        <v>84.24875</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W79" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="X79" t="n">
+        <v>-0.7537313432835822</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0.9299999999999926</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0.01100461483848059</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>-1.868421052631579</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>-0.3599999999999994</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>-0.004195804195804231</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK79" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
